--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487138_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487138_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.5005</v>
+        <v>10.913</v>
       </c>
       <c r="E2" t="n">
-        <v>9.592700000000001</v>
+        <v>10.3531</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9078000000000001</v>
+        <v>0.5598</v>
       </c>
       <c r="G2" t="n">
         <v>8.885400000000001</v>
@@ -610,13 +610,13 @@
         <v>2.7021</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2148</v>
+        <v>0.1976</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1303</v>
+        <v>-0.3698</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9154</v>
+        <v>0.5674</v>
       </c>
       <c r="V2" t="n">
         <v>0.2859</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.4984</v>
+        <v>5.7115</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1246</v>
+        <v>3.2842</v>
       </c>
       <c r="F3" t="n">
-        <v>2.3737</v>
+        <v>2.4273</v>
       </c>
       <c r="G3" t="n">
         <v>2.628</v>
@@ -688,13 +688,13 @@
         <v>1.7371</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2142</v>
+        <v>0.4273</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0462</v>
+        <v>0.1134</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2604</v>
+        <v>0.3139</v>
       </c>
       <c r="V3" t="n">
         <v>1.8842</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. VICUÑA ROYO</t>
+          <t>A. ARBIZU MAIZA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6013</v>
+        <v>2.3141</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6352</v>
+        <v>1.2594</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0339</v>
+        <v>1.0547</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8436</v>
+        <v>2.4734</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4088</v>
+        <v>-0.7761</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4348</v>
+        <v>3.2495</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5842</v>
+        <v>3.5143</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7295</v>
+        <v>0.3726</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8547</v>
+        <v>3.1417</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7406</v>
+        <v>-1.0409</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3207</v>
+        <v>-1.1487</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4199</v>
+        <v>0.1078</v>
       </c>
       <c r="P4" t="n">
-        <v>1.9301</v>
+        <v>0.193</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9301</v>
+        <v>2.1231</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0556</v>
+        <v>-0.3523</v>
       </c>
       <c r="T4" t="n">
-        <v>1.051</v>
+        <v>-0.3249</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0046</v>
+        <v>-0.0275</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. ARBIZU MAIZA</t>
+          <t>J. ARRIAZU ARBIZU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3815</v>
+        <v>2.1331</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3</v>
+        <v>2.6738</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0815</v>
+        <v>-0.5407</v>
       </c>
       <c r="G5" t="n">
-        <v>2.4734</v>
+        <v>1.6518</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7761</v>
+        <v>1.2626</v>
       </c>
       <c r="I5" t="n">
-        <v>3.2495</v>
+        <v>0.3891</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5143</v>
+        <v>1.7521</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3726</v>
+        <v>1.63</v>
       </c>
       <c r="L5" t="n">
-        <v>3.1417</v>
+        <v>0.1221</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.0409</v>
+        <v>-0.1003</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.1487</v>
+        <v>-0.3674</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1078</v>
+        <v>0.267</v>
       </c>
       <c r="P5" t="n">
-        <v>0.193</v>
+        <v>0.579</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1231</v>
+        <v>0.579</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2849</v>
+        <v>0.2304</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2842</v>
+        <v>0.0218</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0007</v>
+        <v>0.2085</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.3281</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.8999</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. ARRIAZU ARBIZU</t>
+          <t>I. VICUÑA ROYO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.906</v>
+        <v>1.6455</v>
       </c>
       <c r="E6" t="n">
-        <v>2.4735</v>
+        <v>1.6526</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5675</v>
+        <v>-0.0071</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6518</v>
+        <v>0.8436</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2626</v>
+        <v>0.4088</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3891</v>
+        <v>0.4348</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7521</v>
+        <v>1.5842</v>
       </c>
       <c r="K6" t="n">
-        <v>1.63</v>
+        <v>0.7295</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1221</v>
+        <v>0.8547</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1003</v>
+        <v>-0.7406</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3674</v>
+        <v>-0.3207</v>
       </c>
       <c r="O6" t="n">
-        <v>0.267</v>
+        <v>-0.4199</v>
       </c>
       <c r="P6" t="n">
-        <v>0.579</v>
+        <v>1.9301</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.579</v>
+        <v>1.9301</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0033</v>
+        <v>0.0998</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1785</v>
+        <v>0.0684</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1818</v>
+        <v>0.0314</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3281</v>
+        <v>-1.228</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8999</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>-1.228</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1939</v>
+        <v>1.0858</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3983</v>
+        <v>1.317</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2044</v>
+        <v>-0.2311</v>
       </c>
       <c r="G7" t="n">
         <v>2.4481</v>
@@ -1000,13 +1000,13 @@
         <v>1.5441</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3893</v>
+        <v>-0.4974</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5221</v>
+        <v>-0.6035</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1328</v>
+        <v>0.1061</v>
       </c>
       <c r="V7" t="n">
         <v>-0.2859</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1373</v>
+        <v>-0.3177</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1231</v>
+        <v>-1.2232</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9858</v>
+        <v>0.9055</v>
       </c>
       <c r="G8" t="n">
         <v>1.9756</v>
@@ -1078,13 +1078,13 @@
         <v>1.158</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4964</v>
+        <v>0.3159</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1057</v>
+        <v>-0.2059</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6021</v>
+        <v>0.5218</v>
       </c>
       <c r="V8" t="n">
         <v>0.2859</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. GARCIA IBAÑEZ</t>
+          <t>K. ABU SHAMS SANCHEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6766</v>
+        <v>-0.7437</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8499</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1732</v>
+        <v>-0.6441</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0207</v>
+        <v>-0.7478</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1128</v>
+        <v>-0.1551</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1335</v>
+        <v>-0.5926</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6469</v>
+        <v>0.1398</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6469</v>
+        <v>0.5796</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.4398</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6676</v>
+        <v>-0.8875</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5341</v>
+        <v>-0.7347</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1335</v>
+        <v>-0.1528</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.965</v>
+        <v>1.158</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.965</v>
+        <v>-0.193</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.3511</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2677</v>
+        <v>0.074</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.238</v>
+        <v>-0.0462</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5056</v>
+        <v>0.1203</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>K. ABU SHAMS SANCHEZ</t>
+          <t>A. GARCIA IBAÑEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0173</v>
+        <v>-0.8105</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.159</v>
+        <v>-1.8499</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8583</v>
+        <v>1.0394</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7478</v>
+        <v>0.0207</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1551</v>
+        <v>-0.1128</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5926</v>
+        <v>0.1335</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1398</v>
+        <v>-0.6469</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5796</v>
+        <v>-0.6469</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.4398</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8875</v>
+        <v>0.6676</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7347</v>
+        <v>0.5341</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1528</v>
+        <v>0.1335</v>
       </c>
       <c r="P10" t="n">
-        <v>1.158</v>
+        <v>-0.965</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.193</v>
+        <v>-0.965</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3511</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1996</v>
+        <v>0.1338</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1057</v>
+        <v>-0.238</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0939</v>
+        <v>0.3718</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. ECHEONDO LACALLE</t>
+          <t>J. ZHANG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8277</v>
+        <v>-1.4721</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0329</v>
+        <v>-2.2867</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7948</v>
+        <v>0.8147</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.5098</v>
+        <v>-1.9989</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.3941</v>
+        <v>-0.8393</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1157</v>
+        <v>-1.1595</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6019</v>
+        <v>-1.8921</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6262</v>
+        <v>-0.6055</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0243</v>
+        <v>-1.2866</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9079</v>
+        <v>-0.1067</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7679</v>
+        <v>-0.2338</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.14</v>
+        <v>0.1271</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>0.772</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.193</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.193</v>
+        <v>0.772</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3179</v>
+        <v>-0.2452</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.238</v>
+        <v>-0.3946</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.08</v>
+        <v>0.1494</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. ZHANG</t>
+          <t>I. ECHEONDO LACALLE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.946</v>
+        <v>-1.6473</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.5465</v>
+        <v>-0.9327</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6005</v>
+        <v>-0.7145</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.9989</v>
+        <v>-1.5098</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.8393</v>
+        <v>-1.3941</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.1595</v>
+        <v>-0.1157</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.8921</v>
+        <v>-0.6019</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.6055</v>
+        <v>-0.6262</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.2866</v>
+        <v>0.0243</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1067</v>
+        <v>-0.9079</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2338</v>
+        <v>-0.7679</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1271</v>
+        <v>-0.14</v>
       </c>
       <c r="P12" t="n">
-        <v>0.772</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-0.193</v>
       </c>
       <c r="R12" t="n">
-        <v>0.772</v>
+        <v>0.193</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7191</v>
+        <v>-0.1375</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6544</v>
+        <v>-0.1378</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0648</v>
+        <v>0.0003</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.0902</v>
+        <v>-3.8304</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.456</v>
+        <v>-0.1962</v>
       </c>
       <c r="F13" t="n">
         <v>-3.6342</v>
@@ -1468,10 +1468,10 @@
         <v>1.3511</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.579</v>
+        <v>-0.3193</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8328</v>
+        <v>-0.5731000000000001</v>
       </c>
       <c r="U13" t="n">
         <v>0.2538</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>14.3865</v>
+        <v>14.98129999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>13.3569</v>
+        <v>13.9519</v>
       </c>
       <c r="F14" t="n">
-        <v>1.029399999999999</v>
+        <v>1.029700000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>17.6848</v>
+        <v>17.68480000000001</v>
       </c>
       <c r="H14" t="n">
         <v>6.142800000000001</v>
@@ -1525,13 +1525,13 @@
         <v>15.5597</v>
       </c>
       <c r="L14" t="n">
-        <v>9.700200000000001</v>
+        <v>9.700200000000002</v>
       </c>
       <c r="M14" t="n">
-        <v>-7.575</v>
+        <v>-7.574999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>-9.417100000000001</v>
+        <v>-9.4171</v>
       </c>
       <c r="O14" t="n">
         <v>1.8419</v>
@@ -1546,13 +1546,13 @@
         <v>15.4407</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6673999999999997</v>
+        <v>-0.07289999999999996</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.2849</v>
+        <v>-2.6902</v>
       </c>
       <c r="U14" t="n">
-        <v>2.6171</v>
+        <v>2.6172</v>
       </c>
       <c r="V14" t="n">
         <v>-5.5259</v>
@@ -1561,7 +1561,7 @@
         <v>3.9276</v>
       </c>
       <c r="X14" t="n">
-        <v>-9.4536</v>
+        <v>-9.453600000000002</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.5966</v>
+        <v>4.3521</v>
       </c>
       <c r="E15" t="n">
-        <v>6.4763</v>
+        <v>6.7767</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.8796</v>
+        <v>-2.4246</v>
       </c>
       <c r="G15" t="n">
         <v>0.7834</v>
@@ -1624,13 +1624,13 @@
         <v>2.5091</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7079</v>
+        <v>0.0476</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.924</v>
+        <v>-0.6236</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2161</v>
+        <v>0.6712</v>
       </c>
       <c r="V15" t="n">
         <v>2.1701</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3586</v>
+        <v>-0.2386</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6044</v>
+        <v>1.8046</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.9629</v>
+        <v>-2.0432</v>
       </c>
       <c r="G17" t="n">
         <v>-1.278</v>
@@ -1780,13 +1780,13 @@
         <v>2.3161</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1276</v>
+        <v>-0.0076</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6861</v>
+        <v>-0.4858</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5585</v>
+        <v>0.4782</v>
       </c>
       <c r="V17" t="n">
         <v>2.784</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2087</v>
+        <v>-0.8012</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5024</v>
+        <v>-0.2019</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7063</v>
+        <v>-0.5992</v>
       </c>
       <c r="G18" t="n">
         <v>-0.701</v>
@@ -1858,13 +1858,13 @@
         <v>1.158</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7006</v>
+        <v>-0.2931</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8923</v>
+        <v>-0.5919</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1917</v>
+        <v>0.2987</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9559</v>
+        <v>-1.9955</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7406</v>
+        <v>0.5404</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.6965</v>
+        <v>-2.5359</v>
       </c>
       <c r="G19" t="n">
         <v>-1.1123</v>
@@ -1936,13 +1936,13 @@
         <v>0.386</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4772</v>
+        <v>0.4376</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4442</v>
+        <v>0.2439</v>
       </c>
       <c r="U19" t="n">
-        <v>0.033</v>
+        <v>0.1937</v>
       </c>
       <c r="V19" t="n">
         <v>-1.5138</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. DIAGNE</t>
+          <t>L. SANCHEZ TURRION</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0973</v>
+        <v>-2.526</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0234</v>
+        <v>-3.2317</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.1207</v>
+        <v>0.7057</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.7469</v>
+        <v>-2.8464</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0104</v>
+        <v>-1.0049</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.7365</v>
+        <v>-1.8414</v>
       </c>
       <c r="J20" t="n">
-        <v>1.8176</v>
+        <v>-2.5262</v>
       </c>
       <c r="K20" t="n">
-        <v>1.6141</v>
+        <v>-0.5641</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2035</v>
+        <v>-1.9621</v>
       </c>
       <c r="M20" t="n">
-        <v>-4.5645</v>
+        <v>-0.3202</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.6245</v>
+        <v>-0.4408</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.94</v>
+        <v>0.1207</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.5441</v>
+        <v>0.386</v>
       </c>
       <c r="Q20" t="n">
-        <v>-4.0532</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.5091</v>
+        <v>0.386</v>
       </c>
       <c r="S20" t="n">
-        <v>0.9657</v>
+        <v>0.3047</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1969</v>
+        <v>-0.3351</v>
       </c>
       <c r="U20" t="n">
-        <v>1.1626</v>
+        <v>0.6398</v>
       </c>
       <c r="V20" t="n">
-        <v>1.228</v>
+        <v>-0.3704</v>
       </c>
       <c r="W20" t="n">
-        <v>2.4559</v>
+        <v>-0.3704</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. SANCHEZ TURRION</t>
+          <t>M. DIAGNE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6192</v>
+        <v>-2.6991</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.432</v>
+        <v>-0.1769</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8127</v>
+        <v>-2.5223</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.8464</v>
+        <v>-2.7469</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.0049</v>
+        <v>-1.0104</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.8414</v>
+        <v>-1.7365</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.5262</v>
+        <v>1.8176</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.5641</v>
+        <v>1.6141</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.9621</v>
+        <v>0.2035</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.3202</v>
+        <v>-4.5645</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4408</v>
+        <v>-2.6245</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1207</v>
+        <v>-1.94</v>
       </c>
       <c r="P21" t="n">
-        <v>0.386</v>
+        <v>-1.5441</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-4.0532</v>
       </c>
       <c r="R21" t="n">
-        <v>0.386</v>
+        <v>2.5091</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2115</v>
+        <v>0.3639</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5354</v>
+        <v>-0.3972</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7469</v>
+        <v>0.7611</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3704</v>
+        <v>1.228</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.3704</v>
+        <v>2.4559</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3028</v>
+        <v>-4.1819</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.692</v>
+        <v>-2.8922</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6109</v>
+        <v>-1.2897</v>
       </c>
       <c r="G22" t="n">
         <v>-2.9571</v>
@@ -2170,13 +2170,13 @@
         <v>1.158</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5737</v>
+        <v>-0.4528</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0462</v>
+        <v>-0.2465</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5275</v>
+        <v>-0.2062</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.2543</v>
+        <v>-6.11</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.2687</v>
+        <v>-3.6692</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.9856</v>
+        <v>-2.4407</v>
       </c>
       <c r="G23" t="n">
         <v>-6.6403</v>
@@ -2248,13 +2248,13 @@
         <v>2.1231</v>
       </c>
       <c r="S23" t="n">
-        <v>1.123</v>
+        <v>0.2674</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2195</v>
+        <v>-0.1811</v>
       </c>
       <c r="U23" t="n">
-        <v>0.9035</v>
+        <v>0.4484</v>
       </c>
       <c r="V23" t="n">
         <v>1.228</v>
@@ -2284,10 +2284,10 @@
         <v>-14.3865</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.0297</v>
+        <v>-1.0295</v>
       </c>
       <c r="F24" t="n">
-        <v>-13.3568</v>
+        <v>-13.3569</v>
       </c>
       <c r="G24" t="n">
         <v>-17.6849</v>
@@ -2326,13 +2326,13 @@
         <v>12.5454</v>
       </c>
       <c r="S24" t="n">
-        <v>0.6676000000000002</v>
+        <v>0.6677</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.6172</v>
+        <v>-2.6173</v>
       </c>
       <c r="U24" t="n">
-        <v>3.2848</v>
+        <v>3.2849</v>
       </c>
       <c r="V24" t="n">
         <v>5.5259</v>
